--- a/output/full_scan/batch_seq1_2026-05-26.xlsx
+++ b/output/full_scan/batch_seq1_2026-05-26.xlsx
@@ -54459,7 +54459,7 @@
         <v>0</v>
       </c>
       <c r="CH188" t="n">
-        <v>213.7275486591082</v>
+        <v>213.7275486591081</v>
       </c>
       <c r="CI188" t="n">
         <v>4.8</v>
